--- a/docs/학부모-핵심정보.xlsx
+++ b/docs/학부모-핵심정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\어영욱\Desktop\my-first-app\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B540E5CE-EAFF-49EC-82F5-6F5C691FD6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0896F6-8F18-47D5-8192-16CE6B588C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="783">
   <si>
     <t>학부모 핵심 정보 — 복지그루</t>
   </si>
@@ -437,7 +437,7 @@
     <t>경상남도</t>
   </si>
   <si>
-    <t>치료지원 — 치료지원 전자카드</t>
+    <t>치료지원 — 치료지원 전자카드 (지침상 「치료지원비 전자카드」)</t>
   </si>
   <si>
     <t>1인당 월 15만 원 한도로 치료지원비를 지원합니다. 전자카드에 매월 충전되거나 영수증으로 청구합니다. 병·의원의 물리치료 · 작업치료 · 청능훈련과, 발달재활치료기관의 언어 · 미술 · 놀이 · 음악재활, 재활심리, 운동 · 감각 · 행동재활, 보행시기능훈련이 대상입니다. 복지부 발달재활서비스는 물리·작업치료를 지원하지 않으므로, 두 제도가 메우는 칸이 다릅니다.</t>
@@ -465,7 +465,7 @@
     <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 통학비 지원」(901000000008) · 「특수교육대상자 숙식비 지원」(901000000009) (경상남도교육청, 2026-08-05 수정)</t>
   </si>
   <si>
-    <t>특기적성교육비 지원 — 특기적성교육비 전자카드 (지침상 「특기적성비지원카드」)</t>
+    <t>특기적성교육비 지원 — 특기적성교육비 전자카드 (지침상 「특기적성교육지원카드」)</t>
   </si>
   <si>
     <t>특수교육대상자로 선정된 아동
@@ -618,19 +618,10 @@
     <t>서식 2</t>
   </si>
   <si>
-    <t>신청처에서 서식을 받아 작성합니다 — 「일반」과 「건강장애」 두 가지로 나뉩니다 (확인 필요)</t>
-  </si>
-  <si>
-    <t>서식 3 (일반) / 서식 4 (건강장애)</t>
-  </si>
-  <si>
-    <t>서식 5</t>
-  </si>
-  <si>
-    <t>서식 6</t>
-  </si>
-  <si>
-    <t>서식 9</t>
+    <t>서식 3·4 (보호자용 / 담임교사용) · 서식 6 (건강장애)</t>
+  </si>
+  <si>
+    <t>서식 13</t>
   </si>
   <si>
     <t>기한과 놓치기 쉬운 갈림길</t>
@@ -2973,7 +2964,7 @@
       </c>
       <c r="B16" s="5">
         <f>COUNTIF('준비 서류'!C:C,"먼저")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
@@ -4350,14 +4341,16 @@
         <v>185</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A26" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C26" s="8"/>
+      <c r="C26" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D26" s="8" t="s">
         <v>158</v>
       </c>
@@ -4365,10 +4358,10 @@
         <v>155</v>
       </c>
       <c r="F26" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
@@ -4389,7 +4382,7 @@
         <v>156</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
@@ -4412,7 +4405,7 @@
         <v>164</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
@@ -4433,7 +4426,7 @@
         <v>166</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
@@ -4475,7 +4468,7 @@
         <v>156</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -4496,7 +4489,7 @@
         <v>166</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
@@ -4538,7 +4531,7 @@
         <v>156</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
@@ -4559,7 +4552,7 @@
         <v>166</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
@@ -4601,7 +4594,7 @@
         <v>156</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
@@ -4645,7 +4638,7 @@
         <v>166</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
@@ -4666,7 +4659,7 @@
         <v>156</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
@@ -4687,7 +4680,7 @@
         <v>166</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
@@ -4730,12 +4723,12 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -4743,10 +4736,10 @@
         <v>143</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -4754,10 +4747,10 @@
         <v>149</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -4765,10 +4758,10 @@
         <v>149</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
@@ -4776,10 +4769,10 @@
         <v>168</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
@@ -4787,10 +4780,10 @@
         <v>168</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
@@ -4798,10 +4791,10 @@
         <v>174</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
@@ -4809,10 +4802,10 @@
         <v>174</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
@@ -4820,10 +4813,10 @@
         <v>177</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
@@ -4831,10 +4824,10 @@
         <v>177</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
@@ -4842,54 +4835,54 @@
         <v>182</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>216</v>
-      </c>
       <c r="C15" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4919,7 +4912,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -4927,16 +4920,16 @@
         <v>31</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>42</v>
@@ -4947,16 +4940,16 @@
         <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>229</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>232</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>53</v>
@@ -4967,16 +4960,16 @@
         <v>127</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>53</v>
@@ -4984,84 +4977,84 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>240</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>241</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>244</v>
       </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>251</v>
       </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -5091,41 +5084,41 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>261</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5133,28 +5126,28 @@
         <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>269</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5162,26 +5155,26 @@
         <v>44</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5189,26 +5182,26 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5216,28 +5209,28 @@
         <v>44</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="F8" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5245,28 +5238,28 @@
         <v>44</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="F9" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>295</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5274,28 +5267,28 @@
         <v>44</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>299</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5303,28 +5296,28 @@
         <v>44</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="F11" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="H11" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="I11" s="8" t="s">
         <v>306</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5332,28 +5325,28 @@
         <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="H12" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="I12" s="8" t="s">
         <v>312</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5361,28 +5354,28 @@
         <v>44</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="F13" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="H13" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5390,26 +5383,26 @@
         <v>44</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5417,26 +5410,26 @@
         <v>44</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5444,26 +5437,26 @@
         <v>44</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -5471,28 +5464,28 @@
         <v>44</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="G17" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>340</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="158.4" x14ac:dyDescent="0.4">
@@ -5500,28 +5493,28 @@
         <v>44</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>347</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -5529,28 +5522,28 @@
         <v>44</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="F19" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>354</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5558,28 +5551,28 @@
         <v>44</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>359</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5587,26 +5580,26 @@
         <v>44</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5614,28 +5607,28 @@
         <v>44</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>366</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5643,26 +5636,26 @@
         <v>44</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5670,28 +5663,28 @@
         <v>44</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="G24" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>377</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5699,26 +5692,26 @@
         <v>44</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5726,26 +5719,26 @@
         <v>44</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -5753,24 +5746,24 @@
         <v>44</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5778,26 +5771,26 @@
         <v>44</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5805,26 +5798,26 @@
         <v>44</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5832,28 +5825,28 @@
         <v>44</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C30" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="G30" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="H30" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="I30" s="8" t="s">
         <v>404</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5861,28 +5854,28 @@
         <v>44</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G31" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="H31" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>408</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5890,28 +5883,28 @@
         <v>44</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>413</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5919,26 +5912,26 @@
         <v>44</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="171.6" x14ac:dyDescent="0.4">
@@ -5946,26 +5939,26 @@
         <v>44</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="66" x14ac:dyDescent="0.4">
@@ -5973,24 +5966,24 @@
         <v>44</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5998,28 +5991,28 @@
         <v>44</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="I36" s="8" t="s">
         <v>429</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6027,26 +6020,26 @@
         <v>44</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6054,26 +6047,26 @@
         <v>44</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -6081,26 +6074,26 @@
         <v>44</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6108,26 +6101,26 @@
         <v>44</v>
       </c>
       <c r="B40" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>445</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>448</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="66" x14ac:dyDescent="0.4">
@@ -6135,26 +6128,26 @@
         <v>44</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6162,24 +6155,24 @@
         <v>44</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6187,24 +6180,24 @@
         <v>44</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6212,24 +6205,24 @@
         <v>44</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6237,24 +6230,24 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6262,24 +6255,24 @@
         <v>44</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6287,28 +6280,28 @@
         <v>44</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6316,28 +6309,28 @@
         <v>127</v>
       </c>
       <c r="B48" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="F48" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="H48" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>481</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6345,28 +6338,28 @@
         <v>127</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C49" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="G49" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="H49" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="I49" s="8" t="s">
         <v>488</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6374,26 +6367,26 @@
         <v>127</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="I50" s="8" t="s">
         <v>495</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6401,26 +6394,26 @@
         <v>127</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6428,26 +6421,26 @@
         <v>127</v>
       </c>
       <c r="B52" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>503</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>506</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6455,28 +6448,28 @@
         <v>127</v>
       </c>
       <c r="B53" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="E53" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="F53" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G53" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="H53" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="I53" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6484,28 +6477,28 @@
         <v>127</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C54" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G54" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="H54" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>519</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6513,28 +6506,28 @@
         <v>127</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G55" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="H55" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="I55" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6542,28 +6535,28 @@
         <v>127</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C56" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="I56" s="8" t="s">
         <v>528</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6571,26 +6564,26 @@
         <v>127</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6598,26 +6591,26 @@
         <v>127</v>
       </c>
       <c r="B58" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>536</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>539</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6625,28 +6618,28 @@
         <v>127</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6654,26 +6647,26 @@
         <v>127</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6681,26 +6674,26 @@
         <v>127</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6708,26 +6701,26 @@
         <v>127</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6735,26 +6728,26 @@
         <v>127</v>
       </c>
       <c r="B63" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="E63" s="8" t="s">
         <v>556</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>557</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>559</v>
       </c>
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6762,26 +6755,26 @@
         <v>127</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6789,26 +6782,26 @@
         <v>127</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6816,26 +6809,26 @@
         <v>127</v>
       </c>
       <c r="B66" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="E66" s="8" t="s">
         <v>571</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>573</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>574</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6843,26 +6836,26 @@
         <v>127</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6870,28 +6863,28 @@
         <v>127</v>
       </c>
       <c r="B68" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G68" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="H68" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="I68" s="8" t="s">
         <v>584</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6899,26 +6892,26 @@
         <v>127</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6926,26 +6919,26 @@
         <v>127</v>
       </c>
       <c r="B70" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>592</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>595</v>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6953,26 +6946,26 @@
         <v>127</v>
       </c>
       <c r="B71" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="E71" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>601</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6980,28 +6973,28 @@
         <v>127</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C72" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="H72" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="I72" s="8" t="s">
         <v>605</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7009,26 +7002,26 @@
         <v>127</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7036,28 +7029,28 @@
         <v>127</v>
       </c>
       <c r="B74" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G74" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>586</v>
-      </c>
       <c r="H74" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7065,26 +7058,26 @@
         <v>127</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7092,26 +7085,26 @@
         <v>127</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7119,24 +7112,24 @@
         <v>127</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7144,28 +7137,28 @@
         <v>127</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C78" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I78" s="8" t="s">
         <v>628</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="I78" s="8" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7173,28 +7166,28 @@
         <v>127</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C79" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G79" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="H79" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="I79" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="79.2" x14ac:dyDescent="0.4">
@@ -7202,26 +7195,26 @@
         <v>127</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7229,28 +7222,28 @@
         <v>127</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C81" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="H81" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="I81" s="8" t="s">
         <v>642</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="H81" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="I81" s="8" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7258,26 +7251,26 @@
         <v>127</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7285,28 +7278,28 @@
         <v>127</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C83" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I83" s="8" t="s">
         <v>649</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="I83" s="8" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7314,26 +7307,26 @@
         <v>127</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="8" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7341,26 +7334,26 @@
         <v>127</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7368,26 +7361,26 @@
         <v>127</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7395,24 +7388,24 @@
         <v>127</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7420,26 +7413,26 @@
         <v>127</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7447,28 +7440,28 @@
         <v>127</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7476,26 +7469,26 @@
         <v>127</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7503,28 +7496,28 @@
         <v>127</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C91" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I91" s="8" t="s">
         <v>685</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>687</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="H91" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7532,26 +7525,26 @@
         <v>127</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7559,24 +7552,24 @@
         <v>127</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
       <c r="G93" s="8" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7584,26 +7577,26 @@
         <v>127</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7611,28 +7604,28 @@
         <v>127</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C95" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="I95" s="8" t="s">
         <v>700</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>702</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="H95" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7640,26 +7633,26 @@
         <v>127</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7667,24 +7660,24 @@
         <v>127</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
   </sheetData>
@@ -7710,399 +7703,399 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>154</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C5" s="8">
         <v>16</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>157</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C6" s="8">
         <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>185</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C7" s="8">
         <v>16</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>732</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C9" s="8">
         <v>16</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C10" s="8">
         <v>12</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C11" s="8">
         <v>12</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>185</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C12" s="8">
         <v>16</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C13" s="8">
         <v>16</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C14" s="8">
         <v>15</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C15" s="8">
         <v>14</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C16" s="8">
         <v>15</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C17" s="8">
         <v>17</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>185</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C18" s="8">
         <v>10</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C19" s="8">
         <v>17</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C20" s="8">
         <v>16</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G20" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C23" s="5">
         <f>COUNT(C5:C20)</f>
@@ -8111,7 +8104,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C24" s="5">
         <f>MIN(C5:C20)</f>
@@ -8120,7 +8113,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C25" s="5">
         <f>MAX(C5:C20)</f>
@@ -8129,7 +8122,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C26" s="5">
         <f>ROUND(AVERAGE(C5:C20),1)</f>
@@ -8138,7 +8131,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C27" s="5">
         <f>COUNTIF(E5:E20,"서식 1")</f>
@@ -8147,7 +8140,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>

--- a/docs/학부모-핵심정보.xlsx
+++ b/docs/학부모-핵심정보.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\어영욱\Desktop\my-first-app\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0896F6-8F18-47D5-8192-16CE6B588C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8904D714-6B76-4ACD-8435-2FB148CF41B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10212" yWindow="912" windowWidth="12372" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">기한·갈림길!$A$4:$C$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">문의처!$A$4:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'제도 한눈에'!$A$4:$N$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'준비 서류'!$A$4:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'준비 서류'!$A$4:$G$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'지역 자체사업'!$A$4:$I$97</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="810">
   <si>
     <t>학부모 핵심 정보 — 복지그루</t>
   </si>
@@ -543,85 +543,166 @@
     <t>서식 4·5 (보호자용 / 담임교사용)</t>
   </si>
   <si>
+    <t>개인정보 수집·이용 및 제공 동의서</t>
+  </si>
+  <si>
+    <t>신청처에서 서식을 받아 서명합니다 (확인 필요)</t>
+  </si>
+  <si>
+    <t>서식 12</t>
+  </si>
+  <si>
+    <t>주민등록등본</t>
+  </si>
+  <si>
+    <t>읍면동 행정복지센터나 정부24에서 뗍니다 (주민등록번호 뒷자리는 가립니다)</t>
+  </si>
+  <si>
+    <t>장애인복지카드 사본 또는 장애인 증명서 (해당하는 경우: 장애인 등록이 되어 있는 경우)</t>
+  </si>
+  <si>
+    <t>장애인 등록이 되어 있으면 복지카드를 복사하거나, 행정복지센터 · 정부24에서 장애인 증명서를 뗍니다</t>
+  </si>
+  <si>
+    <t>의사 진단서 · 소견서 · 의무기록 사본 · 심리평가 보고서 등 (해당하는 경우: 진단 · 치료 · 검사 기록이 있는 경우)</t>
+  </si>
+  <si>
+    <t>진료 · 검사를 받은 병원이나 치료기관에서 받습니다</t>
+  </si>
+  <si>
+    <t>졸업증명서 또는 졸업예정증명서 (해당하는 경우: 졸업했거나 졸업을 앞둔 경우)</t>
+  </si>
+  <si>
+    <t>졸업했거나 다니는 학교에서 받습니다</t>
+  </si>
+  <si>
+    <t>상급학교 진학 배치</t>
+  </si>
+  <si>
+    <t>상급학교 배치 의뢰자 명단 (엑셀)</t>
+  </si>
+  <si>
+    <t>상급학교 배치 신청서</t>
+  </si>
+  <si>
+    <t>서식 8</t>
+  </si>
+  <si>
+    <t>진학 희망 고등학교 학교장 의견서 (해당하는 경우: 특목고 · 특성화고 · 자사고 · 대안학교에 진학하려는 경우)</t>
+  </si>
+  <si>
+    <t>진학하려는 고등학교의 학교장 의견서를 받아, 지금 다니는 중학교를 통해 냅니다</t>
+  </si>
+  <si>
+    <t>서식 16</t>
+  </si>
+  <si>
+    <t>개별화교육지원팀 회의록 사본 (해당하는 경우: 배치 유형(일반학급 · 특수학급 등)을 바꾸는 경우)</t>
+  </si>
+  <si>
+    <t>학교가 개별화교육지원팀 회의를 열고 회의록을 붙입니다</t>
+  </si>
+  <si>
+    <t>전학 · 재배치</t>
+  </si>
+  <si>
+    <t>재배치(배치변경) 신청서</t>
+  </si>
+  <si>
+    <t>서식 7</t>
+  </si>
+  <si>
+    <t>개별화교육지원팀 회의록 사본 (해당하는 경우: 배치 유형을 바꾸는 경우 (거주지 이전만이면 생략))</t>
+  </si>
+  <si>
+    <t>이전 배치 결과통지서 사본 (해당하는 경우: 다른 시 · 군이나 다른 시 · 도로 전학하는 경우)</t>
+  </si>
+  <si>
+    <t>이전에 받으신 배치 결과통지서를 복사해 오시면 됩니다</t>
+  </si>
+  <si>
+    <t>주민등록등본 (해당하는 경우: 다른 시 · 군이나 다른 시 · 도로 주소를 옮긴 경우)</t>
+  </si>
+  <si>
+    <t>취학유예 · 면제</t>
+  </si>
+  <si>
+    <t>취학유예·면제 승인 신청서</t>
+  </si>
+  <si>
+    <t>서식 10</t>
+  </si>
+  <si>
+    <t>개별화교육지원팀 회의록 사본</t>
+  </si>
+  <si>
+    <t>유예·면제 사유를 증명하는 서류 (해당하는 경우: 질병 · 유학 등 사유를 증명해야 하는 경우)</t>
+  </si>
+  <si>
+    <t>사유에 맞는 서류를 냅니다 — 질병이면 병원 진단서, 유학 · 해외 출국이면 출입국 사실증명서 등</t>
+  </si>
+  <si>
+    <t>재취학</t>
+  </si>
+  <si>
+    <t>재취학 신청서</t>
+  </si>
+  <si>
+    <t>서식 11</t>
+  </si>
+  <si>
+    <t>이전 배치 결과통지서 사본</t>
+  </si>
+  <si>
+    <t>서식 2</t>
+  </si>
+  <si>
+    <t>서식 3·4 (보호자용 / 담임교사용)</t>
+  </si>
+  <si>
     <t>배치 신청서</t>
   </si>
   <si>
-    <t>서식 번호 미확인</t>
-  </si>
-  <si>
     <t>학교장 의견서 또는 장애인증명서·복지카드 중 택 1</t>
   </si>
   <si>
     <t>둘 중 하나를 준비합니다 — 재학(예정) 학교에서 「학교장 의견서」, 또는 읍면동 행정복지센터에서 「장애인증명서·복지카드」</t>
   </si>
   <si>
-    <t>개인정보 수집·이용 및 제공 동의서</t>
-  </si>
-  <si>
-    <t>신청처에서 서식을 받아 서명합니다 (확인 필요)</t>
-  </si>
-  <si>
-    <t>서식 12</t>
-  </si>
-  <si>
-    <t>상급학교 진학 배치</t>
-  </si>
-  <si>
-    <t>상급학교 배치 의뢰자 명단 (엑셀)</t>
-  </si>
-  <si>
-    <t>상급학교 배치 신청서</t>
-  </si>
-  <si>
-    <t>서식 8</t>
-  </si>
-  <si>
-    <t>이전 배치 결과통지서 사본</t>
-  </si>
-  <si>
-    <t>이전에 받으신 배치 결과통지서를 복사해 오시면 됩니다</t>
-  </si>
-  <si>
-    <t>전학 · 재배치</t>
-  </si>
-  <si>
-    <t>재배치(배치변경) 신청서</t>
-  </si>
-  <si>
-    <t>서식 7</t>
-  </si>
-  <si>
-    <t>취학유예 · 면제</t>
-  </si>
-  <si>
-    <t>취학유예·면제 승인 신청서</t>
-  </si>
-  <si>
-    <t>서식 10</t>
-  </si>
-  <si>
-    <t>의사 진단서 (최근 3개월 이내)</t>
-  </si>
-  <si>
-    <t>병원에서 발급받습니다 (최근 3개월 이내)</t>
-  </si>
-  <si>
-    <t>재취학</t>
-  </si>
-  <si>
-    <t>재취학 신청서</t>
-  </si>
-  <si>
-    <t>서식 11</t>
-  </si>
-  <si>
-    <t>서식 2</t>
-  </si>
-  <si>
-    <t>서식 3·4 (보호자용 / 담임교사용) · 서식 6 (건강장애)</t>
-  </si>
-  <si>
     <t>서식 13</t>
+  </si>
+  <si>
+    <t>배치(재배치 · 배치변경) 의뢰자 명단 (엑셀)</t>
+  </si>
+  <si>
+    <t>학교가 취합합니다. 보호자가 준비할 서류가 아닙니다</t>
+  </si>
+  <si>
+    <t>개별화교육지원팀 회의록 사본 (해당하는 경우: 단순 거주지 이전이 아닌 경우)</t>
+  </si>
+  <si>
+    <t>주민등록등본 (해당하는 경우: 거주지를 옮긴 경우 (또는 거주지 확인 증명서))</t>
+  </si>
+  <si>
+    <t>유예(면제) 의뢰자 명단 (엑셀)</t>
+  </si>
+  <si>
+    <t>학교 · 교육지원청이 취합합니다. 보호자가 준비할 서류가 아닙니다</t>
+  </si>
+  <si>
+    <t>개별화교육지원팀 회의록 사본 (해당하는 경우: 학교에 다니고 있는 경우)</t>
+  </si>
+  <si>
+    <t>이전 배치 결과통지서 사본 (해당하는 경우: 이미 배치를 받은 경우)</t>
+  </si>
+  <si>
+    <t>유예·면제 사유를 증명하는 서류</t>
+  </si>
+  <si>
+    <t>재취학 의뢰자 명단 (엑셀)</t>
+  </si>
+  <si>
+    <t>주민등록등본 (해당하는 경우: 해외에서 귀국한 경우 — 귀국 뒤 발행분 (재학 · 성적증명서도 필요))</t>
   </si>
   <si>
     <t>기한과 놓치기 쉬운 갈림길</t>
@@ -2964,7 +3045,7 @@
       </c>
       <c r="B16" s="5">
         <f>COUNTIF('준비 서류'!C:C,"먼저")</f>
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
@@ -3849,7 +3930,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3974,13 +4055,13 @@
         <v>155</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>44</v>
       </c>
@@ -3991,68 +4072,74 @@
         <v>144</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D10" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="8"/>
+        <v>149</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D12" s="8" t="s">
         <v>170</v>
       </c>
@@ -4060,10 +4147,10 @@
         <v>155</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
@@ -4071,20 +4158,20 @@
         <v>44</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -4092,20 +4179,20 @@
         <v>44</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
@@ -4113,20 +4200,20 @@
         <v>44</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
@@ -4134,62 +4221,66 @@
         <v>44</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="8"/>
+        <v>172</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D16" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" s="8"/>
+        <v>172</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D17" s="8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
@@ -4197,22 +4288,20 @@
         <v>44</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>144</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -4220,160 +4309,162 @@
         <v>44</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C23" s="8"/>
+        <v>181</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D23" s="8" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="8" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="8" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="39.6" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A26" s="8" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>144</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="8" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>155</v>
@@ -4382,72 +4473,72 @@
         <v>156</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>144</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="8" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="8" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
@@ -4455,20 +4546,20 @@
         <v>127</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
@@ -4476,41 +4567,43 @@
         <v>127</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A33" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C33" s="8"/>
+        <v>149</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D33" s="8" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
@@ -4518,11 +4611,11 @@
         <v>127</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>155</v>
@@ -4531,28 +4624,30 @@
         <v>156</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A35" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C35" s="8"/>
+        <v>149</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="D35" s="8" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
@@ -4560,20 +4655,20 @@
         <v>127</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
@@ -4581,20 +4676,20 @@
         <v>127</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
@@ -4602,22 +4697,20 @@
         <v>127</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>144</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
@@ -4625,20 +4718,20 @@
         <v>127</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
@@ -4646,20 +4739,20 @@
         <v>127</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
@@ -4667,20 +4760,20 @@
         <v>127</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
@@ -4688,24 +4781,345 @@
         <v>127</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G42" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F43" s="8" t="s">
         <v>162</v>
       </c>
+      <c r="G43" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+      <c r="A45" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+      <c r="A46" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+      <c r="A50" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+      <c r="A51" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+      <c r="A52" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
+      <c r="A57" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>153</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G42" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A4:G57" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4723,12 +5137,12 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -4736,10 +5150,10 @@
         <v>143</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -4747,10 +5161,10 @@
         <v>149</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -4758,131 +5172,131 @@
         <v>149</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -4912,7 +5326,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -4920,16 +5334,16 @@
         <v>31</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>42</v>
@@ -4940,16 +5354,16 @@
         <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>53</v>
@@ -4960,16 +5374,16 @@
         <v>127</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>53</v>
@@ -4977,84 +5391,84 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -5084,41 +5498,41 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5126,28 +5540,28 @@
         <v>44</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5155,26 +5569,26 @@
         <v>44</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5182,26 +5596,26 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5209,28 +5623,28 @@
         <v>44</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5238,28 +5652,28 @@
         <v>44</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5267,28 +5681,28 @@
         <v>44</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5296,28 +5710,28 @@
         <v>44</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5325,28 +5739,28 @@
         <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5354,28 +5768,28 @@
         <v>44</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>287</v>
-      </c>
       <c r="I13" s="8" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5383,26 +5797,26 @@
         <v>44</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5410,26 +5824,26 @@
         <v>44</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5437,26 +5851,26 @@
         <v>44</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -5464,28 +5878,28 @@
         <v>44</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="158.4" x14ac:dyDescent="0.4">
@@ -5493,28 +5907,28 @@
         <v>44</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -5522,28 +5936,28 @@
         <v>44</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5551,28 +5965,28 @@
         <v>44</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5580,26 +5994,26 @@
         <v>44</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5607,28 +6021,28 @@
         <v>44</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5636,26 +6050,26 @@
         <v>44</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5663,28 +6077,28 @@
         <v>44</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5692,26 +6106,26 @@
         <v>44</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5719,26 +6133,26 @@
         <v>44</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -5746,24 +6160,24 @@
         <v>44</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5771,26 +6185,26 @@
         <v>44</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5798,26 +6212,26 @@
         <v>44</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5825,28 +6239,28 @@
         <v>44</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5854,28 +6268,28 @@
         <v>44</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5883,28 +6297,28 @@
         <v>44</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5912,26 +6326,26 @@
         <v>44</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="171.6" x14ac:dyDescent="0.4">
@@ -5939,26 +6353,26 @@
         <v>44</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="66" x14ac:dyDescent="0.4">
@@ -5966,24 +6380,24 @@
         <v>44</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -5991,28 +6405,28 @@
         <v>44</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>429</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6020,26 +6434,26 @@
         <v>44</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6047,26 +6461,26 @@
         <v>44</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="8" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>438</v>
+        <v>465</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="52.8" x14ac:dyDescent="0.4">
@@ -6074,26 +6488,26 @@
         <v>44</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>441</v>
+        <v>468</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6101,26 +6515,26 @@
         <v>44</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="66" x14ac:dyDescent="0.4">
@@ -6128,26 +6542,26 @@
         <v>44</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6155,24 +6569,24 @@
         <v>44</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6180,24 +6594,24 @@
         <v>44</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6205,24 +6619,24 @@
         <v>44</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6230,24 +6644,24 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6255,24 +6669,24 @@
         <v>44</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6280,28 +6694,28 @@
         <v>44</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6309,28 +6723,28 @@
         <v>127</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>481</v>
+        <v>508</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6338,28 +6752,28 @@
         <v>127</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6367,26 +6781,26 @@
         <v>127</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="8" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6394,26 +6808,26 @@
         <v>127</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>499</v>
+        <v>526</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6421,26 +6835,26 @@
         <v>127</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8" t="s">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>506</v>
+        <v>533</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6448,28 +6862,28 @@
         <v>127</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>513</v>
+        <v>540</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6477,28 +6891,28 @@
         <v>127</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>515</v>
+        <v>542</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>516</v>
+        <v>543</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>519</v>
+        <v>546</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6506,28 +6920,28 @@
         <v>127</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>521</v>
+        <v>548</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>524</v>
+        <v>551</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6535,28 +6949,28 @@
         <v>127</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C56" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G56" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>498</v>
-      </c>
       <c r="H56" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6564,26 +6978,26 @@
         <v>127</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6591,26 +7005,26 @@
         <v>127</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>538</v>
+        <v>565</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6618,28 +7032,28 @@
         <v>127</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>539</v>
+        <v>566</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>540</v>
+        <v>567</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>541</v>
+        <v>568</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6647,26 +7061,26 @@
         <v>127</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>543</v>
+        <v>570</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6674,26 +7088,26 @@
         <v>127</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>546</v>
+        <v>573</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="8" t="s">
-        <v>547</v>
+        <v>574</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6701,26 +7115,26 @@
         <v>127</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>549</v>
+        <v>576</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>550</v>
+        <v>577</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8" t="s">
-        <v>551</v>
+        <v>578</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>552</v>
+        <v>579</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6728,26 +7142,26 @@
         <v>127</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>553</v>
+        <v>580</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>554</v>
+        <v>581</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>556</v>
+        <v>583</v>
       </c>
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>558</v>
+        <v>585</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>559</v>
+        <v>586</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6755,26 +7169,26 @@
         <v>127</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8" t="s">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>563</v>
+        <v>590</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6782,26 +7196,26 @@
         <v>127</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>564</v>
+        <v>591</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>567</v>
+        <v>594</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6809,26 +7223,26 @@
         <v>127</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>571</v>
+        <v>598</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="s">
-        <v>572</v>
+        <v>599</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>573</v>
+        <v>600</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>574</v>
+        <v>601</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6836,26 +7250,26 @@
         <v>127</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>575</v>
+        <v>602</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>577</v>
+        <v>604</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="s">
-        <v>578</v>
+        <v>605</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6863,28 +7277,28 @@
         <v>127</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6892,26 +7306,26 @@
         <v>127</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="s">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>588</v>
+        <v>615</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6919,26 +7333,26 @@
         <v>127</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>589</v>
+        <v>616</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>590</v>
+        <v>617</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>591</v>
+        <v>618</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>592</v>
+        <v>619</v>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="s">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>558</v>
+        <v>585</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6946,26 +7360,26 @@
         <v>127</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>595</v>
+        <v>622</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>596</v>
+        <v>623</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>598</v>
+        <v>625</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8" t="s">
-        <v>599</v>
+        <v>626</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>600</v>
+        <v>627</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -6973,28 +7387,28 @@
         <v>127</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>601</v>
+        <v>628</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>602</v>
+        <v>629</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>605</v>
+        <v>632</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7002,26 +7416,26 @@
         <v>127</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>606</v>
+        <v>633</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>607</v>
+        <v>634</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>609</v>
+        <v>636</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7029,28 +7443,28 @@
         <v>127</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="C74" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G74" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="D74" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>583</v>
-      </c>
       <c r="H74" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>612</v>
+        <v>639</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7058,26 +7472,26 @@
         <v>127</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="8" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>614</v>
+        <v>641</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7085,26 +7499,26 @@
         <v>127</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>615</v>
+        <v>642</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>616</v>
+        <v>643</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>616</v>
+        <v>643</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>617</v>
+        <v>644</v>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8" t="s">
-        <v>618</v>
+        <v>645</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>619</v>
+        <v>646</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7112,24 +7526,24 @@
         <v>127</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>622</v>
+        <v>649</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>624</v>
+        <v>651</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7137,28 +7551,28 @@
         <v>127</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>626</v>
+        <v>653</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>628</v>
+        <v>655</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7166,28 +7580,28 @@
         <v>127</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>629</v>
+        <v>656</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>630</v>
+        <v>657</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>631</v>
+        <v>658</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>632</v>
+        <v>659</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="79.2" x14ac:dyDescent="0.4">
@@ -7195,26 +7609,26 @@
         <v>127</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>634</v>
+        <v>661</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>635</v>
+        <v>662</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>637</v>
+        <v>664</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7222,28 +7636,28 @@
         <v>127</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>639</v>
+        <v>666</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>640</v>
+        <v>667</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>641</v>
+        <v>668</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>642</v>
+        <v>669</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7251,26 +7665,26 @@
         <v>127</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>643</v>
+        <v>670</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="8" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>645</v>
+        <v>672</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7278,28 +7692,28 @@
         <v>127</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>646</v>
+        <v>673</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>649</v>
+        <v>676</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7307,26 +7721,26 @@
         <v>127</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>651</v>
+        <v>678</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="8" t="s">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>653</v>
+        <v>680</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>654</v>
+        <v>681</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7334,26 +7748,26 @@
         <v>127</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>655</v>
+        <v>682</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>657</v>
+        <v>684</v>
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>659</v>
+        <v>686</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>660</v>
+        <v>687</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7361,26 +7775,26 @@
         <v>127</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>661</v>
+        <v>688</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>662</v>
+        <v>689</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>598</v>
+        <v>625</v>
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8" t="s">
-        <v>664</v>
+        <v>691</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>665</v>
+        <v>692</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7388,24 +7802,24 @@
         <v>127</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>553</v>
+        <v>580</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8" t="s">
-        <v>668</v>
+        <v>695</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>669</v>
+        <v>696</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7413,26 +7827,26 @@
         <v>127</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>673</v>
+        <v>700</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7440,28 +7854,28 @@
         <v>127</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>676</v>
+        <v>703</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7469,26 +7883,26 @@
         <v>127</v>
       </c>
       <c r="B90" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>677</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>650</v>
-      </c>
       <c r="D90" s="8" t="s">
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>680</v>
+        <v>707</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>681</v>
+        <v>708</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7496,28 +7910,28 @@
         <v>127</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>682</v>
+        <v>709</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>685</v>
+        <v>712</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7525,26 +7939,26 @@
         <v>127</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>686</v>
+        <v>713</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>687</v>
+        <v>714</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7552,24 +7966,24 @@
         <v>127</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>595</v>
+        <v>622</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
       <c r="G93" s="8" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7577,26 +7991,26 @@
         <v>127</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>615</v>
+        <v>642</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>692</v>
+        <v>719</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>694</v>
+        <v>721</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>696</v>
+        <v>723</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7604,28 +8018,28 @@
         <v>127</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>700</v>
+        <v>727</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7633,26 +8047,26 @@
         <v>127</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>703</v>
+        <v>730</v>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8" t="s">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>704</v>
+        <v>731</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
@@ -7660,24 +8074,24 @@
         <v>127</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>705</v>
+        <v>732</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>707</v>
+        <v>734</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>709</v>
+        <v>736</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>710</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -7703,399 +8117,399 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.600000000000001" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>712</v>
+        <v>739</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>713</v>
+        <v>740</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>714</v>
+        <v>741</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>154</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="C5" s="8">
         <v>16</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>157</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>721</v>
+        <v>748</v>
       </c>
       <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
-        <v>722</v>
+        <v>749</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>723</v>
+        <v>750</v>
       </c>
       <c r="C6" s="8">
         <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>724</v>
+        <v>751</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>721</v>
+        <v>748</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>725</v>
+        <v>752</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="C7" s="8">
         <v>16</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>730</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
       <c r="C9" s="8">
         <v>16</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>737</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>739</v>
+        <v>766</v>
       </c>
       <c r="C10" s="8">
         <v>12</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>740</v>
+        <v>767</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>741</v>
+        <v>768</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>742</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>744</v>
+        <v>771</v>
       </c>
       <c r="C11" s="8">
         <v>12</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>745</v>
+        <v>772</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="C12" s="8">
         <v>16</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>748</v>
+        <v>775</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>749</v>
+        <v>776</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>751</v>
+        <v>778</v>
       </c>
       <c r="C13" s="8">
         <v>16</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>752</v>
+        <v>779</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="C14" s="8">
         <v>15</v>
       </c>
       <c r="D14" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>729</v>
-      </c>
       <c r="G14" s="8" t="s">
-        <v>757</v>
+        <v>784</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>758</v>
+        <v>785</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="C15" s="8">
         <v>14</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>763</v>
+        <v>790</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
       <c r="C16" s="8">
         <v>15</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>748</v>
+        <v>775</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>765</v>
+        <v>792</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
-        <v>766</v>
+        <v>793</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>767</v>
+        <v>794</v>
       </c>
       <c r="C17" s="8">
         <v>17</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="C18" s="8">
         <v>10</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>771</v>
+        <v>798</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>742</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>773</v>
+        <v>800</v>
       </c>
       <c r="C19" s="8">
         <v>17</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>776</v>
+        <v>803</v>
       </c>
       <c r="C20" s="8">
         <v>16</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G20" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
-        <v>777</v>
+        <v>804</v>
       </c>
       <c r="C23" s="5">
         <f>COUNT(C5:C20)</f>
@@ -8104,7 +8518,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
-        <v>778</v>
+        <v>805</v>
       </c>
       <c r="C24" s="5">
         <f>MIN(C5:C20)</f>
@@ -8113,7 +8527,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
-        <v>779</v>
+        <v>806</v>
       </c>
       <c r="C25" s="5">
         <f>MAX(C5:C20)</f>
@@ -8122,7 +8536,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
       <c r="C26" s="5">
         <f>ROUND(AVERAGE(C5:C20),1)</f>
@@ -8131,7 +8545,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
-        <v>781</v>
+        <v>808</v>
       </c>
       <c r="C27" s="5">
         <f>COUNTIF(E5:E20,"서식 1")</f>
@@ -8140,7 +8554,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>782</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>

--- a/docs/학부모-핵심정보.xlsx
+++ b/docs/학부모-핵심정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\어영욱\Desktop\my-first-app\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8904D714-6B76-4ACD-8435-2FB148CF41B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37450D55-99DD-4FB4-8CB7-679F0402907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10212" yWindow="912" windowWidth="12372" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -201,76 +201,6 @@
     <t>강원·경남 교육청 지침 (2026.08 대조 확인)</t>
   </si>
   <si>
-    <t>치료지원 — 마음모아카드</t>
-  </si>
-  <si>
-    <t>특수교육대상자로 선정된 아동</t>
-  </si>
-  <si>
-    <t>병·의원, 장애인복지관, 사설치료실 등에서 받는 치료지원 비용을 1인당 월 16만 원 이내 실소요액으로 지원합니다. 마음모아카드 포인트로 12개월(3월~다음 해 2월) 씁니다. 영아 · 유 · 초 · 중 · 고 · 특수학교(전공과 포함) 특수교육대상자 중 치료지원 대상자로 선정된 학생이 대상이며, 영아는 재택 보육하는 경우만 해당합니다. 복지부 발달재활서비스는 물리·작업치료를 지원하지 않으므로, 두 제도가 메우는 칸이 다릅니다.</t>
-  </si>
-  <si>
-    <t>특수교육지원센터 (이용계획서 등록·승인)</t>
-  </si>
-  <si>
-    <t>• 치료지원기관 이용계획서</t>
-  </si>
-  <si>
-    <t>매년 3월 (대상자 선정 → 이용계획서 등록·승인 → 카드 발급)</t>
-  </si>
-  <si>
-    <t>장애인 등에 대한 특수교육법 제28조 (특수교육 관련서비스), 같은 법 시행령</t>
-  </si>
-  <si>
-    <t>2026.10 공식 원문 대조</t>
-  </si>
-  <si>
-    <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 치료지원」(강원특별자치도교육청, 2026-06-04 수정, 780000000011) · 강원 특수교육지원센터 운영계획 「치료지원 운영 계획」(2026-03-27, gwe.go.kr bbsSn=50566)</t>
-  </si>
-  <si>
-    <t>지원인력 (보조인력) 배치</t>
-  </si>
-  <si>
-    <t>교수학습 활동 · 신변처리 · 급식 · 교내외 활동 · 등하교를 보조하는 인력을 배치합니다. 학부모가 가장 자주 묻는 항목입니다. 다만 선정되면 자동으로 배치되는 것이 아니라 학교장이 통합교육계획에 포함해 신청하고 교육감이 수급 계획에 따라 배치합니다. 배치 여부와 시기는 학교·교육지원청에 확인해야 합니다.</t>
-  </si>
-  <si>
-    <t>소속 학교 → 교육지원청</t>
-  </si>
-  <si>
-    <t>• 지원인력 배치 요청 (소속 학교를 통해)
-• 배치 결과통지서 사본</t>
-  </si>
-  <si>
-    <t>학교장이 통합교육계획에 포함해 신청. 시기는 학교·교육지원청 확인</t>
-  </si>
-  <si>
-    <t>장애인 등에 대한 특수교육법 제28조 제3항, 시행규칙 제5조</t>
-  </si>
-  <si>
-    <t>법제처 찾기쉬운 생활법령정보 「특수교육 관련서비스」 — 지원인력은 교수학습 활동·신변처리·급식·교내외 활동·등하교 보조. 교육감이 수급 계획 수립과 채용·배치를 수행</t>
-  </si>
-  <si>
-    <t>통학비 및 숙식비 지원</t>
-  </si>
-  <si>
-    <t>특수교육대상자의 통학비와 숙식비를 지원합니다. 학년 초 지원 대상자를 정할 때 학교에 신청합니다. 지원 금액은 원문에 적혀 있지 않아 학교에 확인해야 합니다.</t>
-  </si>
-  <si>
-    <t>소속 학교</t>
-  </si>
-  <si>
-    <t>• 학교 신청서 (학년 초 지원 대상자 선정 시)</t>
-  </si>
-  <si>
-    <t>상시 신청 — 보통 학년 초 지원 대상자 선정 때 냅니다</t>
-  </si>
-  <si>
-    <t>장애인 등에 대한 특수교육법 제28조</t>
-  </si>
-  <si>
-    <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 통학비 및 숙식비 지원」(강원특별자치도교육청 행정과, 2026-06-04 수정, 780000000003) — 근거 특수교육법 제28조 제5항. 금액은 원문에 없음</t>
-  </si>
-  <si>
     <t>의료</t>
   </si>
   <si>
@@ -412,6 +342,76 @@
     <t>법제처 찾기쉬운 생활법령정보 「장애수당 및 장애아동수당」 https://www.easylaw.go.kr/CSP/CnpClsMain.laf?popMenu=ov&amp;csmSeq=916&amp;ccfNo=2&amp;cciNo=1&amp;cnpClsNo=2 · 복지로 「장애아동수당」(보건복지부 장애인자립기반과, 2026년 기준) 원문 대조 — 지급액 일치, 전공과 포함·2026 차상위 금액·금융정보 동의서는 원문에서 추가 · 신청 없이 지급은 보건복지부 보도자료(2025.4, list_no=1485524)</t>
   </si>
   <si>
+    <t>치료지원 — 마음모아카드</t>
+  </si>
+  <si>
+    <t>특수교육대상자로 선정된 아동</t>
+  </si>
+  <si>
+    <t>병·의원, 장애인복지관, 사설치료실 등에서 받는 치료지원 비용을 1인당 월 16만 원 이내 실소요액으로 지원합니다. 마음모아카드 포인트로 12개월(3월~다음 해 2월) 씁니다. 영아 · 유 · 초 · 중 · 고 · 특수학교(전공과 포함) 특수교육대상자 중 치료지원 대상자로 선정된 학생이 대상이며, 영아는 재택 보육하는 경우만 해당합니다. 복지부 발달재활서비스는 물리·작업치료를 지원하지 않으므로, 두 제도가 메우는 칸이 다릅니다.</t>
+  </si>
+  <si>
+    <t>특수교육지원센터 (이용계획서 등록·승인)</t>
+  </si>
+  <si>
+    <t>• 치료지원기관 이용계획서</t>
+  </si>
+  <si>
+    <t>매년 3월 (대상자 선정 → 이용계획서 등록·승인 → 카드 발급)</t>
+  </si>
+  <si>
+    <t>장애인 등에 대한 특수교육법 제28조 (특수교육 관련서비스), 같은 법 시행령</t>
+  </si>
+  <si>
+    <t>2026.10 공식 원문 대조</t>
+  </si>
+  <si>
+    <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 치료지원」(강원특별자치도교육청, 2026-06-04 수정, 780000000011) · 강원 특수교육지원센터 운영계획 「치료지원 운영 계획」(2026-03-27, gwe.go.kr bbsSn=50566)</t>
+  </si>
+  <si>
+    <t>지원인력 (보조인력) 배치</t>
+  </si>
+  <si>
+    <t>교수학습 활동 · 신변처리 · 급식 · 교내외 활동 · 등하교를 보조하는 인력을 배치합니다. 학부모가 가장 자주 묻는 항목입니다. 다만 선정되면 자동으로 배치되는 것이 아니라 학교장이 통합교육계획에 포함해 신청하고 교육감이 수급 계획에 따라 배치합니다. 배치 여부와 시기는 학교·교육지원청에 확인해야 합니다.</t>
+  </si>
+  <si>
+    <t>소속 학교 → 교육지원청</t>
+  </si>
+  <si>
+    <t>• 지원인력 배치 요청 (소속 학교를 통해)
+• 배치 결과통지서 사본</t>
+  </si>
+  <si>
+    <t>학교장이 통합교육계획에 포함해 신청. 시기는 학교·교육지원청 확인</t>
+  </si>
+  <si>
+    <t>장애인 등에 대한 특수교육법 제28조 제3항, 시행규칙 제5조</t>
+  </si>
+  <si>
+    <t>법제처 찾기쉬운 생활법령정보 「특수교육 관련서비스」 — 지원인력은 교수학습 활동·신변처리·급식·교내외 활동·등하교 보조. 교육감이 수급 계획 수립과 채용·배치를 수행</t>
+  </si>
+  <si>
+    <t>통학비 및 숙식비 지원</t>
+  </si>
+  <si>
+    <t>특수교육대상자의 통학비와 숙식비를 지원합니다. 학년 초 지원 대상자를 정할 때 학교에 신청합니다. 지원 금액은 원문에 적혀 있지 않아 학교에 확인해야 합니다.</t>
+  </si>
+  <si>
+    <t>소속 학교</t>
+  </si>
+  <si>
+    <t>• 학교 신청서 (학년 초 지원 대상자 선정 시)</t>
+  </si>
+  <si>
+    <t>상시 신청 — 보통 학년 초 지원 대상자 선정 때 냅니다</t>
+  </si>
+  <si>
+    <t>장애인 등에 대한 특수교육법 제28조</t>
+  </si>
+  <si>
+    <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 통학비 및 숙식비 지원」(강원특별자치도교육청 행정과, 2026-06-04 수정, 780000000003) — 근거 특수교육법 제28조 제5항. 금액은 원문에 없음</t>
+  </si>
+  <si>
     <t>방과후학교 지원 — 마음모아카드</t>
   </si>
   <si>
@@ -452,19 +452,6 @@
     <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 치료지원비 지원」(경상남도교육청, 2026-08-10 수정, 901000000012) · 경상남도교육청 특수교육 지원 안내(gne.go.kr q_bbsSn=1568) — 「치료지원 전자카드」 월 15만 원</t>
   </si>
   <si>
-    <t>통학비 지원</t>
-  </si>
-  <si>
-    <t>학교와 집 사이 편도 2km 이상(유 · 초등은 도심지 시내버스 2구간 이상)이고, 학교 통학버스가 아니라 시 · 내외버스나 자가용으로 통학하는 특수교육대상자와 보호자에게 버스 요금 또는 자가용 유류비를 지원합니다. 특수학교 기숙사에 들어간 학생은 조 · 석식 숙식비를 따로 지원합니다(1년 200일 기준).</t>
-  </si>
-  <si>
-    <t>• 통학비 지원 신청서 (학교에서 받음)
-• 가족관계 증빙 (주민등록등본 · 가족관계증명서 등)</t>
-  </si>
-  <si>
-    <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 통학비 지원」(901000000008) · 「특수교육대상자 숙식비 지원」(901000000009) (경상남도교육청, 2026-08-05 수정)</t>
-  </si>
-  <si>
     <t>특기적성교육비 지원 — 특기적성교육비 전자카드 (지침상 「특기적성교육지원카드」)</t>
   </si>
   <si>
@@ -481,6 +468,19 @@
   </si>
   <si>
     <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 특기적성교육비 지원」(경상남도교육청, 2026-08-05 수정, 901000000007) · 경상남도교육청 특수교육 지원 안내(gne.go.kr q_bbsSn=1568) — 2026학년도 월 12만 원</t>
+  </si>
+  <si>
+    <t>통학비 지원</t>
+  </si>
+  <si>
+    <t>학교와 집 사이 편도 2km 이상(유 · 초등은 도심지 시내버스 2구간 이상)이고, 학교 통학버스가 아니라 시 · 내외버스나 자가용으로 통학하는 특수교육대상자와 보호자에게 버스 요금 또는 자가용 유류비를 지원합니다. 특수학교 기숙사에 들어간 학생은 조 · 석식 숙식비를 따로 지원합니다(1년 200일 기준).</t>
+  </si>
+  <si>
+    <t>• 통학비 지원 신청서 (학교에서 받음)
+• 가족관계 증빙 (주민등록등본 · 가족관계증명서 등)</t>
+  </si>
+  <si>
+    <t>행정안전부 「공공서비스(혜택) 정보」 「특수교육대상자 통학비 지원」(901000000008) · 「특수교육대상자 숙식비 지원」(901000000009) (경상남도교육청, 2026-08-05 수정)</t>
   </si>
   <si>
     <t>선정·배치 신청 — 준비 서류</t>
@@ -3215,19 +3215,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="79.2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" ht="66" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="8" t="s">
         <v>56</v>
       </c>
+      <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
         <v>57</v>
       </c>
@@ -3240,270 +3238,272 @@
       <c r="H6" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="I6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="K6" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+        <v>71</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="K7" s="8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="79.2" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="J8" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="K8" s="8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="66" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="E9" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="79.2" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>96</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="79.2" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>106</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
       <c r="K11" s="8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>116</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
       <c r="K12" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>119</v>
@@ -3537,13 +3537,13 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="N13" s="8" t="s">
         <v>126</v>
@@ -3592,293 +3592,293 @@
         <v>127</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D15" s="8" t="s">
         <v>56</v>
       </c>
+      <c r="D15" s="8"/>
       <c r="E15" s="8" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
+        <v>60</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="K15" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
+        <v>71</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="K16" s="8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="79.2" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="K17" s="8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="66" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="8"/>
+        <v>87</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="E18" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="66" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>96</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
       <c r="K19" s="8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="79.2" x14ac:dyDescent="0.4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>106</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
       <c r="K20" s="8" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M20" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
+      <c r="A21" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="92.4" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="H21" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="52.8" x14ac:dyDescent="0.4">
@@ -3889,33 +3889,33 @@
         <v>45</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>138</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>139</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>52</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="N22" s="8" t="s">
         <v>140</v>
